--- a/fixtures/deals/deal-b/incoming/batch-1/Seller/Fwd - closing docs/fin-2025.XLSX
+++ b/fixtures/deals/deal-b/incoming/batch-1/Seller/Fwd - closing docs/fin-2025.XLSX
@@ -398,104 +398,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B16"/>
-  <cols>
-    <col min="1" max="1" width="120.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>SYNTHETIC</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Income Statement</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>SYNTHETIC</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Year-end Income Statement and Balance Sheet</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Simplified training facsimile - never submit to an agency or lender</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Name: Quenby Grounds Management LLC</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Period: 2025</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Record: fin-2025</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Address: 14 Velnoric Way, Tazmervale, ZZ 00000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Contact: fixture@example.com | (202) 555-0142</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>revenue: 1400000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>net income: 140000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Signature: e-signed; Date: 2026-08-31</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Electronic signature envelope: SYNTHETIC-deal-b-fin-2025</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Signer: Quenby Grounds Management LLC</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Prepared from synthetic documents. For lender review only.</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>SYNTHETIC - For lender review only</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B17"/>
   <cols>
     <col min="1" max="1" width="120.83203125" customWidth="1"/>
@@ -507,7 +409,7 @@
         <v>SYNTHETIC</v>
       </c>
       <c r="B1" t="str">
-        <v>Balance Sheet</v>
+        <v>Income Statement</v>
       </c>
     </row>
     <row r="2">
@@ -542,42 +444,42 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Address: 14 Velnoric Way, Tazmervale, ZZ 00000</v>
+        <v>Document date: 2026-08-31</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Contact: fixture@example.com | (202) 555-0142</v>
+        <v>Address: 14 Velnoric Way, Tazmervale, ZZ 00000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>total assets: 500000</v>
+        <v>Contact: fixture@example.com | (202) 555-0142</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>total liabilities: 100000</v>
+        <v>revenue: 1400000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Signature: e-signed; Date: 2026-08-31</v>
+        <v>net income: 140000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Electronic signature envelope: SYNTHETIC-deal-b-fin-2025</v>
+        <v>Signature: e-signed; Date: 2026-08-31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Signer: Quenby Grounds Management LLC</v>
+        <v>Electronic signature envelope: SYNTHETIC-deal-b-fin-2025</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Equity: 400000</v>
+        <v>Signer: Quenby Grounds Management LLC</v>
       </c>
     </row>
     <row r="16">
@@ -595,4 +497,112 @@
     <ignoredError numberStoredAsText="1" sqref="A1:B17"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B18"/>
+  <cols>
+    <col min="1" max="1" width="120.83203125" customWidth="1"/>
+    <col min="2" max="2" width="25.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>SYNTHETIC</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Balance Sheet</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>SYNTHETIC</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Year-end Income Statement and Balance Sheet</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Simplified training facsimile - never submit to an agency or lender</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Name: Quenby Grounds Management LLC</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Period: 2025</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Record: fin-2025</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Document date: 2026-08-31</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Address: 14 Velnoric Way, Tazmervale, ZZ 00000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Contact: fixture@example.com | (202) 555-0142</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>total assets: 500000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>total liabilities: 100000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Signature: e-signed; Date: 2026-08-31</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Electronic signature envelope: SYNTHETIC-deal-b-fin-2025</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Signer: Quenby Grounds Management LLC</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Equity: 400000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Prepared from synthetic documents. For lender review only.</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>SYNTHETIC - For lender review only</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B18"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/fixtures/deals/deal-b/incoming/batch-1/Seller/Fwd - closing docs/fin-2025.XLSX
+++ b/fixtures/deals/deal-b/incoming/batch-1/Seller/Fwd - closing docs/fin-2025.XLSX
@@ -65,8 +65,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -398,211 +399,324 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B25"/>
   <cols>
-    <col min="1" max="1" width="120.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
+    <col min="1" max="1" width="46.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>SYNTHETIC</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Income Statement</v>
+        <v>Year-end Income Statement and Balance Sheet</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SYNTHETIC</v>
+        <v>Quenby Grounds Management LLC</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Year-end Income Statement and Balance Sheet</v>
+        <v>Statement of Income — for the year ended December 31, 2025</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Simplified training facsimile - never submit to an agency or lender</v>
+        <v>Name: Quenby Grounds Management LLC</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Name: Quenby Grounds Management LLC</v>
+        <v>Period: 2025</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Period: 2025</v>
+        <v>Document date: 08/31/2026</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Record: fin-2025</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Document date: 2026-08-31</v>
+        <v>Compiled by Vale &amp; Reed CPAs LLP. See accountant’s compilation report. Unaudited.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Address: 14 Velnoric Way, Tazmervale, ZZ 00000</v>
+        <v/>
+      </c>
+      <c r="B9" t="str">
+        <v>FY2025</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Contact: fixture@example.com | (202) 555-0142</v>
+        <v>Total revenue</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1400000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>revenue: 1400000</v>
+        <v>Cost of goods sold</v>
+      </c>
+      <c r="B11" s="1">
+        <v>636200</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>net income: 140000</v>
+        <v>Gross profit</v>
+      </c>
+      <c r="B12" s="1">
+        <v>763800</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Signature: e-signed; Date: 2026-08-31</v>
+        <v xml:space="preserve">    Salaries and wages</v>
+      </c>
+      <c r="B13" s="1">
+        <v>361458</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Electronic signature envelope: SYNTHETIC-deal-b-fin-2025</v>
+        <v xml:space="preserve">    Rent</v>
+      </c>
+      <c r="B14" s="1">
+        <v>93278</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Signer: Quenby Grounds Management LLC</v>
+        <v xml:space="preserve">    Utilities</v>
+      </c>
+      <c r="B15" s="1">
+        <v>16323</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Prepared from synthetic documents. For lender review only.</v>
+        <v xml:space="preserve">    Insurance</v>
+      </c>
+      <c r="B16" s="1">
+        <v>24485</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SYNTHETIC - For lender review only</v>
+        <v xml:space="preserve">    Vehicle and fuel</v>
+      </c>
+      <c r="B17" s="1">
+        <v>30315</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v xml:space="preserve">    Depreciation</v>
+      </c>
+      <c r="B18" s="1">
+        <v>34979</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v xml:space="preserve">    Professional fees</v>
+      </c>
+      <c r="B19" s="1">
+        <v>13991</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v xml:space="preserve">    Other operating expenses</v>
+      </c>
+      <c r="B20" s="1">
+        <v>48971</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Total operating expenses</v>
+      </c>
+      <c r="B21" s="1">
+        <v>623800</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Net income</v>
+      </c>
+      <c r="B22" s="1">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Signature: e-signed; Date: 08/31/2026</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>SYNTHETIC SPECIMEN — synthetic test data</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B25"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B21"/>
   <cols>
-    <col min="1" max="1" width="120.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
+    <col min="1" max="1" width="46.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>SYNTHETIC</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Balance Sheet</v>
+        <v>Quenby Grounds Management LLC</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SYNTHETIC</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Year-end Income Statement and Balance Sheet</v>
+        <v>Balance Sheet — December 31, 2025</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Simplified training facsimile - never submit to an agency or lender</v>
+        <v/>
+      </c>
+      <c r="B4" t="str">
+        <v>12/31/2025</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Name: Quenby Grounds Management LLC</v>
+        <v>ASSETS</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Period: 2025</v>
+        <v xml:space="preserve">    Cash</v>
+      </c>
+      <c r="B6" s="1">
+        <v>170000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Record: fin-2025</v>
+        <v xml:space="preserve">    Accounts receivable, net</v>
+      </c>
+      <c r="B7" s="1">
+        <v>120000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Document date: 2026-08-31</v>
+        <v xml:space="preserve">    Inventory</v>
+      </c>
+      <c r="B8" s="1">
+        <v>60000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Address: 14 Velnoric Way, Tazmervale, ZZ 00000</v>
+        <v xml:space="preserve">    Prepaid expenses</v>
+      </c>
+      <c r="B9" s="1">
+        <v>10000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Contact: fixture@example.com | (202) 555-0142</v>
+        <v xml:space="preserve">    Equipment and vehicles, net</v>
+      </c>
+      <c r="B10" s="1">
+        <v>140000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>total assets: 500000</v>
+        <v>Total assets</v>
+      </c>
+      <c r="B11" s="1">
+        <v>500000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>total liabilities: 100000</v>
+        <v>LIABILITIES AND MEMBERS’ EQUITY</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Signature: e-signed; Date: 2026-08-31</v>
+        <v xml:space="preserve">    Accounts payable</v>
+      </c>
+      <c r="B13" s="1">
+        <v>30000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Electronic signature envelope: SYNTHETIC-deal-b-fin-2025</v>
+        <v xml:space="preserve">    Accrued liabilities</v>
+      </c>
+      <c r="B14" s="1">
+        <v>15000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Signer: Quenby Grounds Management LLC</v>
+        <v xml:space="preserve">    Current portion of long-term debt</v>
+      </c>
+      <c r="B15" s="1">
+        <v>10000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Equity: 400000</v>
+        <v xml:space="preserve">    Long-term debt, less current portion</v>
+      </c>
+      <c r="B16" s="1">
+        <v>45000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Prepared from synthetic documents. For lender review only.</v>
+        <v>Total liabilities</v>
+      </c>
+      <c r="B17" s="1">
+        <v>100000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SYNTHETIC - For lender review only</v>
+        <v xml:space="preserve">    Members’ equity</v>
+      </c>
+      <c r="B18" s="1">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Total liabilities and members’ equity</v>
+      </c>
+      <c r="B19" s="1">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>SYNTHETIC SPECIMEN — synthetic test data</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B21"/>
   </ignoredErrors>
 </worksheet>
 </file>